--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.166.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.166.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.166" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.22250.166" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.166.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.22250\oocihm.22250.166.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.22250\0166.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0166.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -875,7 +875,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.166.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.166.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.22250.166" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.22250.166" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y75"/>
+  <dimension ref="A1:Y81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L22: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Answerâ€”Continued.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]159</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]159</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 159</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L35: isolated marker/symbol line :: +</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]159</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,12 +668,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L25: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 46 â€” 47</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: APPEARANCE - - â€¢</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: APPEARANCE - - •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -681,13 +685,13 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: 20</t>
+          <t>L35: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L96: punctuation artifact: repeated periods :: The first proceeding in a suit ..........</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: APPEARANCE - - •</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
@@ -723,12 +727,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L40: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 23 â€” 113</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 22â€”23</t>
+          <t>L65: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -740,13 +744,13 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 21</t>
+          <t>L37: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L109: punctuation artifact: repeated periods :: English authorities, .............................</t>
+          <t>L96: punctuation artifact: repeated periods :: The first proceeding in a suit ..........</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -766,7 +770,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -780,14 +784,10 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L87: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 21 â€” 22</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 46â€”47</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -799,13 +799,13 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 22</t>
+          <t>L39: isolated marker/symbol line :: 21</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L166: punctuation artifact: repeated periods :: plemental Bills, ...........................</t>
+          <t>L109: punctuation artifact: repeated periods :: English authorities, .............................</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
@@ -839,14 +839,10 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L96: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 22 â€” 23</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L100: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -858,11 +854,15 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: *</t>
+          <t>L43: isolated marker/symbol line :: 22</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
-      <c r="Q6" s="1" t="inlineStr"/>
+      <c r="Q6" s="1" t="inlineStr">
+        <is>
+          <t>L166: punctuation artifact: repeated periods :: plemental Bills, ...........................</t>
+        </is>
+      </c>
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr"/>
       <c r="T6" s="1" t="inlineStr"/>
@@ -894,14 +894,10 @@
       <c r="G7" s="1" t="inlineStr"/>
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 23â€”113</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -913,7 +909,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L49: isolated marker/symbol line :: 44</t>
+          <t>L45: symbol-only separator/garbage line :: 22—23</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -949,14 +945,10 @@
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
-      <c r="J8" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 23 â€” 113</t>
-        </is>
-      </c>
+      <c r="J8" s="1" t="inlineStr"/>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L187: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -968,7 +960,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L51: isolated marker/symbol line :: 45</t>
+          <t>L47: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1007,7 +999,7 @@
       <c r="J9" s="1" t="inlineStr"/>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 31â€”32</t>
+          <t>L189: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1019,7 +1011,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 46</t>
+          <t>L49: isolated marker/symbol line :: 44</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1041,12 +1033,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1058,7 +1050,7 @@
       <c r="J10" s="1" t="inlineStr"/>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L86: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 32â€”33</t>
+          <t>L190: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1070,7 +1062,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 46</t>
+          <t>L51: isolated marker/symbol line :: 45</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1097,7 +1089,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1107,21 +1099,17 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L22: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L22: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: 46</t>
+          <t>L53: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1143,12 +1131,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>80</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>58</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1158,11 +1146,7 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1172,7 +1156,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 47</t>
+          <t>L55: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1199,7 +1183,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1209,21 +1193,17 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 41â€”42</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L26: isolated marker/symbol line :: +</t>
+          <t>L25: symbol-only separator/garbage line :: 46 — 47</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L63: symbol-only separator/garbage line :: . 108</t>
+          <t>L57: isolated marker/symbol line :: 46</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1260,21 +1240,17 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L170: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 21â€”22</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L27: isolated marker/symbol line :: 23</t>
+          <t>L26: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L65: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L59: symbol-only separator/garbage line :: . 46—47</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1311,21 +1287,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L176: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 22â€”23</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L29: isolated marker/symbol line :: 47</t>
+          <t>L27: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 23</t>
+          <t>L61: isolated marker/symbol line :: 47</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1362,21 +1334,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L187: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: 23</t>
+          <t>L29: isolated marker/symbol line :: 47</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 23</t>
+          <t>L63: symbol-only separator/garbage line :: . 108</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1413,21 +1381,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L32: symbol-only separator/garbage line :: . 108</t>
+          <t>L30: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L71: isolated marker/symbol line :: 24</t>
+          <t>L65: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1452,21 +1416,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L33: isolated marker/symbol line :: .</t>
+          <t>L32: symbol-only separator/garbage line :: . 108</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 24</t>
+          <t>L67: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1496,12 +1456,12 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 24</t>
+          <t>L33: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L69: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1531,12 +1491,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L37: isolated marker/symbol line :: 24</t>
+          <t>L34: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 31</t>
+          <t>L71: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1566,12 +1526,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: V</t>
+          <t>L37: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L73: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1601,12 +1561,12 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L47: isolated marker/symbol line :: 31</t>
+          <t>L40: symbol-only separator/garbage line :: 23 — 113</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L75: symbol-only separator/garbage line :: 23—113</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1636,12 +1596,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: 110</t>
+          <t>L42: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: f.</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1671,12 +1631,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L50: symbol-only separator/garbage line :: 31-32</t>
+          <t>L47: isolated marker/symbol line :: 31</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: 110</t>
+          <t>L84: isolated marker/symbol line :: 31</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1706,12 +1666,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L52: symbol-only separator/garbage line :: 32-33</t>
+          <t>L48: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L113: symbol-only separator/garbage line :: . 40</t>
+          <t>L85: symbol-only separator/garbage line :: 31—32</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1741,12 +1701,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 40</t>
+          <t>L50: symbol-only separator/garbage line :: 31-32</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L114: isolated marker/symbol line :: 40</t>
+          <t>L86: symbol-only separator/garbage line :: 32—33</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1776,12 +1736,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: 32</t>
+          <t>L52: symbol-only separator/garbage line :: 32-33</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L115: symbol-only separator/garbage line :: . 40</t>
+          <t>L100: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1811,12 +1771,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 40</t>
+          <t>L53: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L117: symbol-only separator/garbage line :: . 41</t>
+          <t>L102: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1846,12 +1806,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: 40</t>
+          <t>L55: isolated marker/symbol line :: 32</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L119: symbol-only separator/garbage line :: .41</t>
+          <t>L104: isolated marker/symbol line :: f.</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1881,12 +1841,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 155</t>
+          <t>L56: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: 41</t>
+          <t>L111: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1916,12 +1876,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: 41</t>
+          <t>L57: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L122: symbol-only separator/garbage line :: . 41</t>
+          <t>L113: symbol-only separator/garbage line :: . 40</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1951,12 +1911,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 41</t>
+          <t>L60: isolated marker/symbol line :: 155</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 41</t>
+          <t>L114: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1986,12 +1946,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: 18</t>
+          <t>L61: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: 42</t>
+          <t>L115: symbol-only separator/garbage line :: . 40</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2021,12 +1981,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: 41</t>
+          <t>L62: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L132: symbol-only separator/garbage line :: . 42</t>
+          <t>L117: symbol-only separator/garbage line :: . 41</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2056,12 +2016,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: 41</t>
+          <t>L65: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L134: isolated marker/symbol line :: 43</t>
+          <t>L119: symbol-only separator/garbage line :: .41</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2091,12 +2051,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 18</t>
+          <t>L66: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L135: symbol-only separator/garbage line :: . 43</t>
+          <t>L121: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2126,12 +2086,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: 41</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: 43</t>
+          <t>L122: symbol-only separator/garbage line :: . 41</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2161,12 +2121,12 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 19</t>
+          <t>L69: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L143: isolated marker/symbol line :: 32</t>
+          <t>L124: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2196,12 +2156,12 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L75: symbol-only separator/garbage line :: 41-42</t>
+          <t>L70: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L145: symbol-only separator/garbage line :: . 155</t>
+          <t>L126: symbol-only separator/garbage line :: 41—42</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2231,12 +2191,12 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 20</t>
+          <t>L72: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L147: isolated marker/symbol line :: 18</t>
+          <t>L130: isolated marker/symbol line :: 42</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr"/>
@@ -2266,12 +2226,12 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: 42</t>
+          <t>L73: isolated marker/symbol line :: 19</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L149: isolated marker/symbol line :: 18</t>
+          <t>L132: symbol-only separator/garbage line :: . 42</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr"/>
@@ -2301,12 +2261,12 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: 6</t>
+          <t>L75: symbol-only separator/garbage line :: 41-42</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L151: isolated marker/symbol line :: 19</t>
+          <t>L134: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr"/>
@@ -2336,12 +2296,12 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 42</t>
+          <t>L76: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L153: isolated marker/symbol line :: 20</t>
+          <t>L135: symbol-only separator/garbage line :: . 43</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr"/>
@@ -2371,12 +2331,12 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: 43</t>
+          <t>L81: isolated marker/symbol line :: 42</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L174: isolated marker/symbol line :: 22</t>
+          <t>L139: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr"/>
@@ -2406,12 +2366,12 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 43</t>
+          <t>L83: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L178: isolated marker/symbol line :: 23</t>
+          <t>L143: isolated marker/symbol line :: 32</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr"/>
@@ -2441,12 +2401,12 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 6</t>
+          <t>L84: isolated marker/symbol line :: 42</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L180: isolated marker/symbol line :: 4</t>
+          <t>L145: symbol-only separator/garbage line :: . 155</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr"/>
@@ -2476,12 +2436,12 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 22</t>
+          <t>L86: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L187: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L147: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr"/>
@@ -2511,12 +2471,12 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 43</t>
+          <t>L87: symbol-only separator/garbage line :: 21 — 22</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L189: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L149: isolated marker/symbol line :: 18</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr"/>
@@ -2546,12 +2506,12 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 23</t>
+          <t>L89: isolated marker/symbol line :: 43</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L190: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L151: isolated marker/symbol line :: 19</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr"/>
@@ -2581,12 +2541,12 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 20</t>
+          <t>L90: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L192: isolated marker/symbol line :: -</t>
+          <t>L153: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr"/>
@@ -2616,10 +2576,14 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: 21</t>
-        </is>
-      </c>
-      <c r="O51" s="1" t="inlineStr"/>
+          <t>L93: isolated marker/symbol line :: 22</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr">
+        <is>
+          <t>L170: symbol-only separator/garbage line :: 21—22</t>
+        </is>
+      </c>
       <c r="P51" s="1" t="inlineStr"/>
       <c r="Q51" s="1" t="inlineStr"/>
       <c r="R51" s="1" t="inlineStr"/>
@@ -2647,10 +2611,14 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="O52" s="1" t="inlineStr"/>
+          <t>L95: isolated marker/symbol line :: 43</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr">
+        <is>
+          <t>L174: isolated marker/symbol line :: 22</t>
+        </is>
+      </c>
       <c r="P52" s="1" t="inlineStr"/>
       <c r="Q52" s="1" t="inlineStr"/>
       <c r="R52" s="1" t="inlineStr"/>
@@ -2678,10 +2646,14 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 22</t>
-        </is>
-      </c>
-      <c r="O53" s="1" t="inlineStr"/>
+          <t>L96: symbol-only separator/garbage line :: 22 — 23</t>
+        </is>
+      </c>
+      <c r="O53" s="1" t="inlineStr">
+        <is>
+          <t>L176: symbol-only separator/garbage line :: 22—23</t>
+        </is>
+      </c>
       <c r="P53" s="1" t="inlineStr"/>
       <c r="Q53" s="1" t="inlineStr"/>
       <c r="R53" s="1" t="inlineStr"/>
@@ -2709,10 +2681,14 @@
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L106: symbol-only separator/garbage line :: 22-23</t>
-        </is>
-      </c>
-      <c r="O54" s="1" t="inlineStr"/>
+          <t>L99: isolated marker/symbol line :: 23</t>
+        </is>
+      </c>
+      <c r="O54" s="1" t="inlineStr">
+        <is>
+          <t>L178: isolated marker/symbol line :: 23</t>
+        </is>
+      </c>
       <c r="P54" s="1" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr"/>
       <c r="R54" s="1" t="inlineStr"/>
@@ -2740,10 +2716,14 @@
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: +</t>
-        </is>
-      </c>
-      <c r="O55" s="1" t="inlineStr"/>
+          <t>L101: isolated marker/symbol line :: 20</t>
+        </is>
+      </c>
+      <c r="O55" s="1" t="inlineStr">
+        <is>
+          <t>L180: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
       <c r="P55" s="1" t="inlineStr"/>
       <c r="Q55" s="1" t="inlineStr"/>
       <c r="R55" s="1" t="inlineStr"/>
@@ -2771,10 +2751,14 @@
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L108: isolated marker/symbol line :: 23</t>
-        </is>
-      </c>
-      <c r="O56" s="1" t="inlineStr"/>
+          <t>L102: isolated marker/symbol line :: 21</t>
+        </is>
+      </c>
+      <c r="O56" s="1" t="inlineStr">
+        <is>
+          <t>L187: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P56" s="1" t="inlineStr"/>
       <c r="Q56" s="1" t="inlineStr"/>
       <c r="R56" s="1" t="inlineStr"/>
@@ -2802,10 +2786,14 @@
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L109: isolated marker/symbol line :: .</t>
-        </is>
-      </c>
-      <c r="O57" s="1" t="inlineStr"/>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="O57" s="1" t="inlineStr">
+        <is>
+          <t>L189: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P57" s="1" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr"/>
       <c r="R57" s="1" t="inlineStr"/>
@@ -2833,10 +2821,14 @@
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: 23</t>
-        </is>
-      </c>
-      <c r="O58" s="1" t="inlineStr"/>
+          <t>L105: isolated marker/symbol line :: 22</t>
+        </is>
+      </c>
+      <c r="O58" s="1" t="inlineStr">
+        <is>
+          <t>L190: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="P58" s="1" t="inlineStr"/>
       <c r="Q58" s="1" t="inlineStr"/>
       <c r="R58" s="1" t="inlineStr"/>
@@ -2864,10 +2856,14 @@
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: 24</t>
-        </is>
-      </c>
-      <c r="O59" s="1" t="inlineStr"/>
+          <t>L106: symbol-only separator/garbage line :: 22-23</t>
+        </is>
+      </c>
+      <c r="O59" s="1" t="inlineStr">
+        <is>
+          <t>L192: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P59" s="1" t="inlineStr"/>
       <c r="Q59" s="1" t="inlineStr"/>
       <c r="R59" s="1" t="inlineStr"/>
@@ -2895,7 +2891,7 @@
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L113: isolated marker/symbol line :: 24</t>
+          <t>L107: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -2926,7 +2922,7 @@
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: 40</t>
+          <t>L108: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -2957,7 +2953,7 @@
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 40</t>
+          <t>L109: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -2988,7 +2984,7 @@
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: 40</t>
+          <t>L110: isolated marker/symbol line :: 23</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3019,7 +3015,7 @@
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 41</t>
+          <t>L111: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3050,7 +3046,7 @@
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L119: isolated marker/symbol line :: 41</t>
+          <t>L113: isolated marker/symbol line :: 24</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3081,7 +3077,7 @@
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L120: isolated marker/symbol line :: 41</t>
+          <t>L114: symbol-only separator/garbage line :: 23 — 113</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3112,7 +3108,7 @@
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: 41</t>
+          <t>L115: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3143,7 +3139,7 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: 41</t>
+          <t>L116: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3174,7 +3170,7 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L123: symbol-only separator/garbage line :: 41-42</t>
+          <t>L117: isolated marker/symbol line :: 40</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3205,7 +3201,7 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L125: isolated marker/symbol line :: 42</t>
+          <t>L118: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3236,7 +3232,7 @@
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: 42</t>
+          <t>L119: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -3267,7 +3263,7 @@
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: 43</t>
+          <t>L120: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -3298,7 +3294,7 @@
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L128: isolated marker/symbol line :: 43</t>
+          <t>L121: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -3329,7 +3325,7 @@
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: 43</t>
+          <t>L122: isolated marker/symbol line :: 41</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -3360,7 +3356,7 @@
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L134: isolated marker/symbol line :: 110</t>
+          <t>L123: symbol-only separator/garbage line :: 41-42</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -3375,6 +3371,192 @@
       <c r="X75" s="1" t="inlineStr"/>
       <c r="Y75" s="1" t="inlineStr"/>
     </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr"/>
+      <c r="B76" s="1" t="inlineStr"/>
+      <c r="C76" s="1" t="inlineStr"/>
+      <c r="D76" s="1" t="inlineStr"/>
+      <c r="E76" s="1" t="inlineStr"/>
+      <c r="F76" s="1" t="inlineStr"/>
+      <c r="G76" s="1" t="inlineStr"/>
+      <c r="H76" s="1" t="inlineStr"/>
+      <c r="I76" s="1" t="inlineStr"/>
+      <c r="J76" s="1" t="inlineStr"/>
+      <c r="K76" s="1" t="inlineStr"/>
+      <c r="L76" s="1" t="inlineStr"/>
+      <c r="M76" s="1" t="inlineStr"/>
+      <c r="N76" s="1" t="inlineStr">
+        <is>
+          <t>L125: isolated marker/symbol line :: 42</t>
+        </is>
+      </c>
+      <c r="O76" s="1" t="inlineStr"/>
+      <c r="P76" s="1" t="inlineStr"/>
+      <c r="Q76" s="1" t="inlineStr"/>
+      <c r="R76" s="1" t="inlineStr"/>
+      <c r="S76" s="1" t="inlineStr"/>
+      <c r="T76" s="1" t="inlineStr"/>
+      <c r="U76" s="1" t="inlineStr"/>
+      <c r="V76" s="1" t="inlineStr"/>
+      <c r="W76" s="1" t="inlineStr"/>
+      <c r="X76" s="1" t="inlineStr"/>
+      <c r="Y76" s="1" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr"/>
+      <c r="B77" s="1" t="inlineStr"/>
+      <c r="C77" s="1" t="inlineStr"/>
+      <c r="D77" s="1" t="inlineStr"/>
+      <c r="E77" s="1" t="inlineStr"/>
+      <c r="F77" s="1" t="inlineStr"/>
+      <c r="G77" s="1" t="inlineStr"/>
+      <c r="H77" s="1" t="inlineStr"/>
+      <c r="I77" s="1" t="inlineStr"/>
+      <c r="J77" s="1" t="inlineStr"/>
+      <c r="K77" s="1" t="inlineStr"/>
+      <c r="L77" s="1" t="inlineStr"/>
+      <c r="M77" s="1" t="inlineStr"/>
+      <c r="N77" s="1" t="inlineStr">
+        <is>
+          <t>L126: isolated marker/symbol line :: 42</t>
+        </is>
+      </c>
+      <c r="O77" s="1" t="inlineStr"/>
+      <c r="P77" s="1" t="inlineStr"/>
+      <c r="Q77" s="1" t="inlineStr"/>
+      <c r="R77" s="1" t="inlineStr"/>
+      <c r="S77" s="1" t="inlineStr"/>
+      <c r="T77" s="1" t="inlineStr"/>
+      <c r="U77" s="1" t="inlineStr"/>
+      <c r="V77" s="1" t="inlineStr"/>
+      <c r="W77" s="1" t="inlineStr"/>
+      <c r="X77" s="1" t="inlineStr"/>
+      <c r="Y77" s="1" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr"/>
+      <c r="B78" s="1" t="inlineStr"/>
+      <c r="C78" s="1" t="inlineStr"/>
+      <c r="D78" s="1" t="inlineStr"/>
+      <c r="E78" s="1" t="inlineStr"/>
+      <c r="F78" s="1" t="inlineStr"/>
+      <c r="G78" s="1" t="inlineStr"/>
+      <c r="H78" s="1" t="inlineStr"/>
+      <c r="I78" s="1" t="inlineStr"/>
+      <c r="J78" s="1" t="inlineStr"/>
+      <c r="K78" s="1" t="inlineStr"/>
+      <c r="L78" s="1" t="inlineStr"/>
+      <c r="M78" s="1" t="inlineStr"/>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t>L127: isolated marker/symbol line :: 43</t>
+        </is>
+      </c>
+      <c r="O78" s="1" t="inlineStr"/>
+      <c r="P78" s="1" t="inlineStr"/>
+      <c r="Q78" s="1" t="inlineStr"/>
+      <c r="R78" s="1" t="inlineStr"/>
+      <c r="S78" s="1" t="inlineStr"/>
+      <c r="T78" s="1" t="inlineStr"/>
+      <c r="U78" s="1" t="inlineStr"/>
+      <c r="V78" s="1" t="inlineStr"/>
+      <c r="W78" s="1" t="inlineStr"/>
+      <c r="X78" s="1" t="inlineStr"/>
+      <c r="Y78" s="1" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr"/>
+      <c r="B79" s="1" t="inlineStr"/>
+      <c r="C79" s="1" t="inlineStr"/>
+      <c r="D79" s="1" t="inlineStr"/>
+      <c r="E79" s="1" t="inlineStr"/>
+      <c r="F79" s="1" t="inlineStr"/>
+      <c r="G79" s="1" t="inlineStr"/>
+      <c r="H79" s="1" t="inlineStr"/>
+      <c r="I79" s="1" t="inlineStr"/>
+      <c r="J79" s="1" t="inlineStr"/>
+      <c r="K79" s="1" t="inlineStr"/>
+      <c r="L79" s="1" t="inlineStr"/>
+      <c r="M79" s="1" t="inlineStr"/>
+      <c r="N79" s="1" t="inlineStr">
+        <is>
+          <t>L128: isolated marker/symbol line :: 43</t>
+        </is>
+      </c>
+      <c r="O79" s="1" t="inlineStr"/>
+      <c r="P79" s="1" t="inlineStr"/>
+      <c r="Q79" s="1" t="inlineStr"/>
+      <c r="R79" s="1" t="inlineStr"/>
+      <c r="S79" s="1" t="inlineStr"/>
+      <c r="T79" s="1" t="inlineStr"/>
+      <c r="U79" s="1" t="inlineStr"/>
+      <c r="V79" s="1" t="inlineStr"/>
+      <c r="W79" s="1" t="inlineStr"/>
+      <c r="X79" s="1" t="inlineStr"/>
+      <c r="Y79" s="1" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr"/>
+      <c r="B80" s="1" t="inlineStr"/>
+      <c r="C80" s="1" t="inlineStr"/>
+      <c r="D80" s="1" t="inlineStr"/>
+      <c r="E80" s="1" t="inlineStr"/>
+      <c r="F80" s="1" t="inlineStr"/>
+      <c r="G80" s="1" t="inlineStr"/>
+      <c r="H80" s="1" t="inlineStr"/>
+      <c r="I80" s="1" t="inlineStr"/>
+      <c r="J80" s="1" t="inlineStr"/>
+      <c r="K80" s="1" t="inlineStr"/>
+      <c r="L80" s="1" t="inlineStr"/>
+      <c r="M80" s="1" t="inlineStr"/>
+      <c r="N80" s="1" t="inlineStr">
+        <is>
+          <t>L130: isolated marker/symbol line :: 43</t>
+        </is>
+      </c>
+      <c r="O80" s="1" t="inlineStr"/>
+      <c r="P80" s="1" t="inlineStr"/>
+      <c r="Q80" s="1" t="inlineStr"/>
+      <c r="R80" s="1" t="inlineStr"/>
+      <c r="S80" s="1" t="inlineStr"/>
+      <c r="T80" s="1" t="inlineStr"/>
+      <c r="U80" s="1" t="inlineStr"/>
+      <c r="V80" s="1" t="inlineStr"/>
+      <c r="W80" s="1" t="inlineStr"/>
+      <c r="X80" s="1" t="inlineStr"/>
+      <c r="Y80" s="1" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr"/>
+      <c r="B81" s="1" t="inlineStr"/>
+      <c r="C81" s="1" t="inlineStr"/>
+      <c r="D81" s="1" t="inlineStr"/>
+      <c r="E81" s="1" t="inlineStr"/>
+      <c r="F81" s="1" t="inlineStr"/>
+      <c r="G81" s="1" t="inlineStr"/>
+      <c r="H81" s="1" t="inlineStr"/>
+      <c r="I81" s="1" t="inlineStr"/>
+      <c r="J81" s="1" t="inlineStr"/>
+      <c r="K81" s="1" t="inlineStr"/>
+      <c r="L81" s="1" t="inlineStr"/>
+      <c r="M81" s="1" t="inlineStr"/>
+      <c r="N81" s="1" t="inlineStr">
+        <is>
+          <t>L134: isolated marker/symbol line :: 110</t>
+        </is>
+      </c>
+      <c r="O81" s="1" t="inlineStr"/>
+      <c r="P81" s="1" t="inlineStr"/>
+      <c r="Q81" s="1" t="inlineStr"/>
+      <c r="R81" s="1" t="inlineStr"/>
+      <c r="S81" s="1" t="inlineStr"/>
+      <c r="T81" s="1" t="inlineStr"/>
+      <c r="U81" s="1" t="inlineStr"/>
+      <c r="V81" s="1" t="inlineStr"/>
+      <c r="W81" s="1" t="inlineStr"/>
+      <c r="X81" s="1" t="inlineStr"/>
+      <c r="Y81" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
